--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{692C95D5-51F2-4311-AF32-433E7E28CAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C090AC-3CE8-459F-BD78-5E0FDF5BFF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8B11E0ED-0CAB-4AC2-A3EA-9AF0BF2F62BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E3721669-D6C4-4E30-A13C-D6B8043BEE80}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -857,7 +857,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{1E5ABE5B-C143-46AF-A44F-343CDC6BA8E5}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{67497933-B43E-4420-903E-A38E016153AC}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -891,10 +891,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="79896" name="Picture 1">
+        <xdr:cNvPr id="79904" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9A1F7E-C555-CD7E-91EF-B1AF5862BEF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D85E720-2B52-5537-9B8B-7F6342431C74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -968,7 +968,7 @@
         <xdr:cNvPr id="3" name="Straight Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7122CBA2-13A9-D488-303C-6BB0379B0081}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94557C1F-26A7-80DA-9411-F357EDBF5EC4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1018,7 +1018,7 @@
         <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D439A7EA-76D2-04AE-805C-ACD94A4BA2FA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2305DB45-0ECB-3761-9340-C1B8587DBA7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1065,10 +1065,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="79899" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
+        <xdr:cNvPr id="79907" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68770F73-6EDC-78A9-1DBA-A1FDDF5AC894}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5206749-FB0D-8665-BAC4-11C4E1538573}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4980003D-A9CA-4A6E-8195-2BAB9D44EEA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61BD705F-D7DD-4569-8D56-EBDC89D32A8F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95445F3B-BE9F-4755-8EF3-55997B2570E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C9A778-2FCE-4ACA-967B-0395097E8668}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2640,7 +2640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480F84C8-3D50-4710-938F-EA5FFB67EEEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465FF875-A22B-4870-A939-36CBF17C758C}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2950,7 +2950,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{482B3F9C-FAD6-43D1-8E5F-C093E8BFB265}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C665E6D-E9F4-4809-886F-545F50770145}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C090AC-3CE8-459F-BD78-5E0FDF5BFF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C834CD-51E4-44E3-98A8-30640E664D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E3721669-D6C4-4E30-A13C-D6B8043BEE80}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{05F96469-9E9F-460A-B213-4782FBF25155}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -857,7 +857,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{67497933-B43E-4420-903E-A38E016153AC}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{FE5C88EF-8684-4787-8316-D883845144BA}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -879,22 +879,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
+      <xdr:colOff>53340</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>198120</xdr:colOff>
+      <xdr:colOff>160020</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="79904" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D85E720-2B52-5537-9B8B-7F6342431C74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23B5BDB2-25ED-6766-F56C-4345461D4FCC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -917,8 +917,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="68580" y="83820"/>
-          <a:ext cx="5539740" cy="1264920"/>
+          <a:off x="53340" y="68580"/>
+          <a:ext cx="5516880" cy="1257300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -953,22 +953,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>481965</xdr:colOff>
+      <xdr:colOff>379095</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>262890</xdr:rowOff>
+      <xdr:rowOff>201930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>346942</xdr:colOff>
+      <xdr:colOff>287885</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>262890</xdr:rowOff>
+      <xdr:rowOff>201930</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="3" name="Straight Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94557C1F-26A7-80DA-9411-F357EDBF5EC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3210EFD5-F1AD-B255-EE65-EE43A2D91735}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1005,20 +1005,20 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>264795</xdr:rowOff>
+      <xdr:rowOff>211455</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>346721</xdr:colOff>
+      <xdr:colOff>287708</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>264795</xdr:rowOff>
+      <xdr:rowOff>211455</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2305DB45-0ECB-3761-9340-C1B8587DBA7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3438B16-3BA6-401C-2F97-B9C02DAC4670}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1059,16 +1059,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:colOff>1341120</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="79907" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5206749-FB0D-8665-BAC4-11C4E1538573}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34DBE4B6-FF75-F3DE-F798-C5089665E3F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1079,7 +1079,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="8945880"/>
-          <a:ext cx="2560320" cy="563880"/>
+          <a:ext cx="2225040" cy="556260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1371,7 +1371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61BD705F-D7DD-4569-8D56-EBDC89D32A8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C3C62B-841B-4825-A01F-6F34B67378C8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C9A778-2FCE-4ACA-967B-0395097E8668}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B6479D-93EA-4162-9B08-CC03FFA14651}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2640,7 +2640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465FF875-A22B-4870-A939-36CBF17C758C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAD6D52-6F31-40D1-AF0A-8194A411586D}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2950,7 +2950,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C665E6D-E9F4-4809-886F-545F50770145}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99BF389-0667-447D-950D-B9796171F2DD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C834CD-51E4-44E3-98A8-30640E664D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86EEBF11-E007-4BA8-9D87-AEE8B2441F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{05F96469-9E9F-460A-B213-4782FBF25155}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9CB475F-2F96-4E03-BE16-575A67C3DFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>LINE</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>shipper </t>
+  </si>
+  <si>
+    <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
   </si>
 </sst>
 </file>
@@ -857,7 +860,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{FE5C88EF-8684-4787-8316-D883845144BA}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{A30F4BFF-C573-4291-AB49-9AF46BB67300}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -891,10 +894,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="79904" name="Picture 1">
+        <xdr:cNvPr id="79908" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23B5BDB2-25ED-6766-F56C-4345461D4FCC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35CB9D1A-102B-CDCD-5FE8-1BA555E0352B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -968,7 +971,7 @@
         <xdr:cNvPr id="3" name="Straight Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3210EFD5-F1AD-B255-EE65-EE43A2D91735}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C4A5B22-0DD3-6CBF-48E0-2752AA5E2CAE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1018,7 +1021,7 @@
         <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3438B16-3BA6-401C-2F97-B9C02DAC4670}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE1E74D-E78B-FA1D-FD80-32D7BE91BD5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1065,10 +1068,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="79907" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
+        <xdr:cNvPr id="79911" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34DBE4B6-FF75-F3DE-F798-C5089665E3F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C0993E9-94F2-6DEE-FDC4-7C546A2F2321}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C3C62B-841B-4825-A01F-6F34B67378C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57C3FC7-10F5-4D90-8B67-67219002AFF8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1928,7 +1931,9 @@
       <c r="V28" s="31"/>
     </row>
     <row r="29" spans="1:22" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="70"/>
+      <c r="A29" s="70" t="s">
+        <v>45</v>
+      </c>
       <c r="B29" s="71"/>
       <c r="C29" s="71"/>
       <c r="D29" s="71"/>
@@ -2501,7 +2506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B6479D-93EA-4162-9B08-CC03FFA14651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4513D7-1B81-43C2-AED8-FA619BFC1D6C}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2640,7 +2645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAD6D52-6F31-40D1-AF0A-8194A411586D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B188952-24BF-4CCE-A169-9C5053B986FF}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2950,7 +2955,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99BF389-0667-447D-950D-B9796171F2DD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{766CF833-5AA3-44B1-847C-D5BEBC183F68}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86EEBF11-E007-4BA8-9D87-AEE8B2441F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89488D64-5FCF-4EF7-8C08-968102A66AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9CB475F-2F96-4E03-BE16-575A67C3DFC1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F017ECC-DBD9-4E80-90A8-B09BE421628F}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -860,7 +860,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{A30F4BFF-C573-4291-AB49-9AF46BB67300}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{4C27F989-80D1-4101-9CA1-59E95988620A}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -897,7 +897,7 @@
         <xdr:cNvPr id="79908" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35CB9D1A-102B-CDCD-5FE8-1BA555E0352B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD39BCE-F09F-1C94-F08C-14C2B16578CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -971,7 +971,7 @@
         <xdr:cNvPr id="3" name="Straight Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C4A5B22-0DD3-6CBF-48E0-2752AA5E2CAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62CAA9A0-B80F-C767-12AC-ACC493C11C24}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1021,7 +1021,7 @@
         <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE1E74D-E78B-FA1D-FD80-32D7BE91BD5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{097D7F6B-8CD5-2E24-9EF3-9DCCA3FCE8E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1071,7 +1071,7 @@
         <xdr:cNvPr id="79911" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C0993E9-94F2-6DEE-FDC4-7C546A2F2321}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DE076F4-BAE7-02E5-4C58-0C0AE37227BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1374,7 +1374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57C3FC7-10F5-4D90-8B67-67219002AFF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC600B5C-787B-4BA4-8664-90F9F4E30B18}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2506,7 +2506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4513D7-1B81-43C2-AED8-FA619BFC1D6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508AD5A3-962D-4E14-804D-16291F26D6AB}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2645,7 +2645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B188952-24BF-4CCE-A169-9C5053B986FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F2D9E1-E269-41B9-9394-852B3661AD9A}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2955,7 +2955,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{766CF833-5AA3-44B1-847C-D5BEBC183F68}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F10A91-D423-4819-A38E-F0E621188754}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89488D64-5FCF-4EF7-8C08-968102A66AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEFD64E5-30E8-48A5-A1AC-4FF2455D6CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F017ECC-DBD9-4E80-90A8-B09BE421628F}"/>
+    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{29F101F6-38CC-4638-9801-49D29A8134B3}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>LINE</t>
   </si>
@@ -91,12 +91,6 @@
     <t>NAME / ชื่อ :</t>
   </si>
   <si>
-    <t xml:space="preserve">TEL / โทรศัพท์ :   </t>
-  </si>
-  <si>
-    <t>Agent :</t>
-  </si>
-  <si>
     <t>Date / Time</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>PAYMENT TAEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHIPPING / ตัวแทน / ผู้ส่งออก </t>
   </si>
   <si>
     <r>
@@ -133,9 +124,6 @@
     <t>TYPE</t>
   </si>
   <si>
-    <t>HEUNG-A LINE (THAILAND) CO.,LTD</t>
-  </si>
-  <si>
     <t>Compatibility Report for NEW SHORE  HUTCHISON (A2).xls</t>
   </si>
   <si>
@@ -188,6 +176,12 @@
   </si>
   <si>
     <t>***** อนุญาตให้ลูกค้ากรอกรายละเอียดในฟอร์ม ช. เองได้ หากผิดผลาดใดๆลูกค้าจะเป็นคนรับผิดชอบทุกประการ *****</t>
+  </si>
+  <si>
+    <t>EMAIL :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL / โทร :   </t>
   </si>
 </sst>
 </file>
@@ -860,7 +854,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{4C27F989-80D1-4101-9CA1-59E95988620A}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{42BBA60A-BC6C-46EC-BBD0-78F86B83D571}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -888,16 +882,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
+      <xdr:colOff>167640</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="79908" name="Picture 1">
+        <xdr:cNvPr id="79912" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD39BCE-F09F-1C94-F08C-14C2B16578CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38144E0F-23F6-06F6-7536-EB69BD36AC06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -921,7 +915,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="53340" y="68580"/>
-          <a:ext cx="5516880" cy="1257300"/>
+          <a:ext cx="5524500" cy="1249680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -953,106 +947,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>379095</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>201930</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>287885</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>201930</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62CAA9A0-B80F-C767-12AC-ACC493C11C24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="714375" y="9315450"/>
-          <a:ext cx="2095500" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>211455</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>287708</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>211455</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{097D7F6B-8CD5-2E24-9EF3-9DCCA3FCE8E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="962025" y="9582150"/>
-          <a:ext cx="1562100" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1062,16 +956,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1341120</xdr:colOff>
+      <xdr:colOff>1348740</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="79911" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
+        <xdr:cNvPr id="79913" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DE076F4-BAE7-02E5-4C58-0C0AE37227BD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1340F589-FDC7-27A5-0869-40ED9433DCEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1082,7 +976,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="8945880"/>
-          <a:ext cx="2225040" cy="556260"/>
+          <a:ext cx="2232660" cy="556260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1374,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC600B5C-787B-4BA4-8664-90F9F4E30B18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2F2B5A-475A-482A-9B1D-25C80E623DA5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1417,13 +1311,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>2</v>
@@ -1435,7 +1329,7 @@
         <v>9</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>11</v>
@@ -1444,7 +1338,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>4</v>
@@ -1468,7 +1362,7 @@
         <v>13</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V9" s="11" t="s">
         <v>14</v>
@@ -1932,7 +1826,7 @@
     </row>
     <row r="29" spans="1:22" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="70" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B29" s="71"/>
       <c r="C29" s="71"/>
@@ -2006,7 +1900,7 @@
     </row>
     <row r="32" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C32" s="14"/>
     </row>
@@ -2022,7 +1916,7 @@
     </row>
     <row r="34" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="15"/>
@@ -2044,11 +1938,9 @@
     </row>
     <row r="35" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -2067,9 +1959,7 @@
       <c r="R35" s="34"/>
     </row>
     <row r="36" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="68" t="s">
-        <v>23</v>
-      </c>
+      <c r="A36" s="68"/>
       <c r="B36" s="69"/>
       <c r="C36" s="69"/>
       <c r="D36" s="69"/>
@@ -2506,37 +2396,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508AD5A3-962D-4E14-804D-16291F26D6AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12BAC0A4-5390-4BF1-9641-82102D714F79}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="F1" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="G1" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="H1" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="I1" s="52" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="52" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -2645,7 +2535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F2D9E1-E269-41B9-9394-852B3661AD9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616DA09A-CF19-435D-BE1A-EBE7D954E630}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2658,7 +2548,7 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B1" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="20"/>
@@ -2667,7 +2557,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="20"/>
@@ -2683,7 +2573,7 @@
     </row>
     <row r="4" spans="2:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B4" s="17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="21"/>
@@ -2699,15 +2589,15 @@
     </row>
     <row r="6" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="20"/>
       <c r="E6" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -2719,7 +2609,7 @@
     </row>
     <row r="8" spans="2:6" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="22"/>
@@ -2727,7 +2617,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -2955,7 +2845,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F10A91-D423-4819-A38E-F0E621188754}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A9AF8F8-0B20-483C-985F-5862CC0F8BC1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEFD64E5-30E8-48A5-A1AC-4FF2455D6CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0552754-4778-4098-831F-0BE87B6731DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{29F101F6-38CC-4638-9801-49D29A8134B3}"/>
+    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{2125A513-9368-42F8-A2F0-05E17876559F}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{42BBA60A-BC6C-46EC-BBD0-78F86B83D571}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{EACC5EE4-F95C-45CD-8539-4F1E4253C429}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -891,7 +891,7 @@
         <xdr:cNvPr id="79912" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38144E0F-23F6-06F6-7536-EB69BD36AC06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E910FBD-79C2-6681-D721-3F3205D393F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +965,7 @@
         <xdr:cNvPr id="79913" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1340F589-FDC7-27A5-0869-40ED9433DCEB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60E966BF-5FB7-0411-6DDC-26EF8C5059ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1268,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2F2B5A-475A-482A-9B1D-25C80E623DA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A4F37A-270E-4A3F-8EC8-BF20EC3DD369}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2396,7 +2396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12BAC0A4-5390-4BF1-9641-82102D714F79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABD7D68-7DC6-4A08-A935-CA438499190D}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2535,7 +2535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616DA09A-CF19-435D-BE1A-EBE7D954E630}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27E09C5-EABD-4F27-989E-71915E44D9B8}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2845,7 +2845,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A9AF8F8-0B20-483C-985F-5862CC0F8BC1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED5A2148-0802-4286-BC36-9918B069B5D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0552754-4778-4098-831F-0BE87B6731DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{218E8CCE-8AE9-4E3A-AD81-14A4EEBC269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{2125A513-9368-42F8-A2F0-05E17876559F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{354E1C75-FA16-478E-80C4-F9667582127E}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{EACC5EE4-F95C-45CD-8539-4F1E4253C429}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{4217DA9D-0EB8-4088-A7DB-A54F6A3E942D}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -891,7 +891,7 @@
         <xdr:cNvPr id="79912" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E910FBD-79C2-6681-D721-3F3205D393F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC59119D-D22F-3B84-B318-7E6736DFEF46}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +965,7 @@
         <xdr:cNvPr id="79913" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60E966BF-5FB7-0411-6DDC-26EF8C5059ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F335453-0BB5-BE9B-51AF-1CC1D6E98ABD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1268,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A4F37A-270E-4A3F-8EC8-BF20EC3DD369}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA54B76-CACA-46D9-9A5A-651145811BAB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2396,7 +2396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABD7D68-7DC6-4A08-A935-CA438499190D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE30B94-6F29-44B6-8036-6928AD061F4A}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2535,7 +2535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27E09C5-EABD-4F27-989E-71915E44D9B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7090C1-D5F7-4446-A064-158C319A0AA9}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2845,7 +2845,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED5A2148-0802-4286-BC36-9918B069B5D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB3A2415-F101-4F86-8398-D4E338A7234B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/docs/templates/A3C1C2-HUTCHISON.xlsx
+++ b/docs/templates/A3C1C2-HUTCHISON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{218E8CCE-8AE9-4E3A-AD81-14A4EEBC269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62ED5515-B852-41EE-98FF-403939802457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{354E1C75-FA16-478E-80C4-F9667582127E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52B118C5-1194-4ACF-99D1-347612C32B63}"/>
   </bookViews>
   <sheets>
     <sheet name="HPT" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{4217DA9D-0EB8-4088-A7DB-A54F6A3E942D}"/>
+    <cellStyle name="Normal_CHORE" xfId="2" xr:uid="{1F0EF677-7BE4-45E3-A812-A03DC937FCD5}"/>
     <cellStyle name="Output" xfId="3" builtinId="21"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
@@ -891,7 +891,7 @@
         <xdr:cNvPr id="79912" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC59119D-D22F-3B84-B318-7E6736DFEF46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9532004F-A0FF-B860-7D46-0162387766A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +965,7 @@
         <xdr:cNvPr id="79913" name="x_Picture 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAOwAAABACAYAAAAZDZuBAAAAAXNSR0IArs4c6QAAIABJREFUeF7tfQeUHMXx/lczG+5QFgooERRAIAzCZGwwJpgMNjLBZBtjcjBBtzOzJ5a7nZ49ARIIhBA2mMxPYMBk/mSJbLJAIkmABCiBAKFw2jBd/9ezM6e51V6QEArW9nt6T7fTsbq/7qrq6ipCJVUoUKHABkMB2mB6WulohQIVCqAC2I18EVx55ZUd3Ky7U0EWti/IwlA37/Z1pRsHIUtMc/Wo/lFVpGp6TOamXZpKfbuRk2udD78C2HU+BWu/A+l0uh8RHbi0epMjFi9esi8tb+xeTYSOVVXo1LEjIrEoNBAKhQKWLl2KxUuWILs82+i67osdO3d8PBKJPJJKpT5b+z2vtFgB7Ea4Bv5y4827RHO5NwYtmINBgwaj3667osvQbdFbB7qF6CEBLF28GD/88AMW/bAIs7+cjZmfzsC8+fPV7w9Ud+xwXSaTeWEjJOE6G3IFsOuM9Ou24c9/s/OoLT+bfgX6bwlsMRAYOAQYsBUweDCw465Az54tdvCrr77CRx9+hA+nT8esWbOfk5BXjh079sl1O6KNo/UKYDeOeS47Su6C99GI7ZEr+dxNB36xA/CbA4HfHgjssx+ga2Xr+HD6h3jjzTcwfdr0p3ONOXvsdWMnb8Qk/dmHXgHsz07i9bcB7o2BgD5zpR7+6AKNoV+36Q8ceyJw3AnAsB3KDmjWrFl4ccqLeG/qe7fHYrGEEGLu+jvyDbdnFcBuuHO3RnrOm0WuAvMlZSvTdCCXAxb6X3UAhx8InHIGcPQxZYvMnDkTk5+fvOyDqR84Y68bm14jnaxU0kSBCmAriwHcW18MoGOrpNB1YGkOWOTn+uVQ4MLLgFP+UrbY9OnT8NSTT30y47OZl4wfP/7RCpnXDAUqgF0zdNyga+Fe2lkgmtCuQSjgui4w3y1m320YMLIWGHFc2eKTJ0/GlClTHpo7d+6oCRMmTG1XG5VMLVKgAtjK4vAowL31rwH0bTc5SoG7/17AqPqigqokLVu2DM899xxefeXVCcsal42+5pprvmh3O2sw4+WXX965Klp1EAh7ArITgPmQ2jNZN/tKKpUqVb2Vbfnee+/VP5sx42/s0odGrdF0pSWEOAPAXNM0f1ZuogmwDfX120hdP48k4pDadYlRiffbopUQ4khi+gOAz7L5bEN7B91WvZXva58C3Es/GYTbV7nlUuCefTqQuQro3HWlqhbMm4+nnnlavv/e+9cszy2/dty4cbNXub3VLJBJiwYmjPSLfw9gGYDNACjJHABdKyFvsSyrVS5A2OJ6As5VJVyW/ZPJ5NciLS4gwrVeLbo2PJFIvLea3WyzWBNgHSGuA+M8r1HGvxJJs7xwEqpS2GIGAYPUTxL8C8uyPmizxUqG9ZYC3NvTGA9crQ5GdWCxL+P27ghkrgZO+1vZqj777DO89OJLhWnTp92XW5a7Y+z1Y58kteraSKlUapMqXT8jp+tvjjLNl9vKr757ppe5/EsMDAf4QWjaSMMwZgRlM7Z9EDPdCsJmYDxqJM0jWqvXsW0BkKHy6NFIn5EjR86zbfsvGuhm9Zsm9e1qams+bE/fVidPE2AzaXElEy4tbja43jDN89uq0LGdVwHewyviaju051Ruq87K9zVLAbXI4/H4ZswcIaJvDMNQp0vZxH30kyFX45QNalNXterE/crnLg87APjnrcBm/cq2N3v2bLz26muYNm3a7EXff/9ytCr+fId4h3ei1dH5mqYtl1LGiGhTHRjuSnnQ8mzuwEWNy3vGO3R498q61E7toZRjiykA9mbgadMyf9dSGUeI+eS6IlFb652UrYLWcQ5m5s9M0/wkyOc4zu/y+fw3o0aNeqet8j/lexNgRVo4REgUK6NrDcu4qK2KHVu8BOBXPmC3T4xKTGtjoIMhcTmDI2C8aibNcW21IYTYVJNokIQOILxjmubotsqo74rFdzV9lNr0CPSsYRn/DJdT9rQRaPWSUE2MrkToxQwCKRaJlgByKhM9lsvlnkmlUsvLtal2VgIdSKD52Xw20VK+oOzo+vohrhYxoaHeMAzPFledAPlc3gHQk4BNCNhc/c4M1ZvlAL/DRE/kcrmn2ityeOKNFjkDxCeD0UtV5zFBRfbPBeMJED2k57OPjkyl5gX9Y7VV99a/A7AyP9seogd5wmxyRx0Ycx1wxtkt1vDdd995llMzZszA3DlzsOjHHznbmM0CiKo+MyTiVVXo1rUrev1qbxz64lPolbpiN8rjjda6JYT4DTGKcibTsUbSuK+l/EKIntFodNlll122NJxHCLE1GJerdVRwC1eNGjXqrbZIIWwxTpPup4na2uuaAF3v7MsaKzlXI3B/gKrJY2bBBPzIhGnE/DhFIi/V1NQorX3ZtHYBazuPAnxYU080GhQs3JY6mLHtQxj0eKjMkDBL01I5R4hnwQg0IHMNy2ymUMnY9kkMusMvP58Yt0FDDBJdmHgQQPsE35gx2kyaY0rbcmyhlCdbqN916W49srb209YmM5POHMUk/8OEw0zT9MZUV1e3a1SP/LepHGEcM6LE6Ajy2FNvQwTwtQQnLcu6tbU2HCGuBeMCLw/hBQbu1qV8h2UkKyNyGwKOBuNPfh0FCT4jXCf30mpBVNfWomzX95gOfOmftkcdBNx4c4unbVBfY2Mjvpm/AN//8AOy2SzUvhWLxdCtWzf06dMH8XgcuLoOuPTyTwnYulVa2HYGoJoiXvFX0zQ9tnVVkmM7NQBnvDqACaZlntNWeccWaoOcaljmjkFeR4i7m+jOeJKBt4koSsw9StabQvE/iN2ra2prPy5ta60BtqGhoZMsuHMAqB08OEXqzKSpdq8Wk23b+2ugZ1ZkYNuwrGSrE+U43SBZtROkNwzL3C1cxkk7I0D87+JvfIVhWanw91QqFYvHYreD4d1XMCNtJs3aZnWEOAxo1OZG4tQ7B0Djp5mwr2manglfQzq9iySteFIwHjeS5ooNTZ3AqSt7FaL5FxEsTqbjjaQxqXT8mUymC1ypADocQF5juU9NMvlaOTo1NDT0lwX3WVWnJjGiptZ8IMjHfdEDrv5NW4uy3d/Dp20XHbj5TmDE8e0uXjbj6SOAWx4Aemln0QI5saXKmullgLcTlrnzqjbspJ3zQOyflNxgWJbPhbZck2OLZQA9Y1jGkUGusLKqpc1dCHEqMdT1WnVxPdC5RtK4IdzSWgOsY9spgBK6dH/hanrA+39pWKYH3pZSg20fKEFPhb5/bVhm/9bKiLS4ggijAP4WoB4AXjcs05O1mwgoxNHEuN/7uxWZPaxYC5QMQR2Obb8I0K/V37p0B4+srV3ZzC/UZjnA2rb9Sw0UsFmTDcvct3RsRVa6iWYLs/lcr1QqpVjc4rwyU0ZkPgR4GwBZl+U2yWRyVms0SqVSHePR+IWGZdil+bi3/hCApsW2qou8bP7waXvaCcD4G4FN1M3KKqbGZUC/zsBSF+im5+G6m9K3KMtCOrZjACyCFohxcyJp/nVVWnTSzjkgHu9T2jEsy2yrfAuAHUeApxfSwL+rsayny9UzZsyY6mxj41PBugIoGZ6jtQhYsZiApxKWOULY4nUCvBOPWP4qkUy+0hIRildHuAegyQAf4i1Qwj6maapTp2zK2EIpVp5jxlYgKOXEagPWsZ2bAfY05qXtri3AqrYdIT4AY5jfj23CCg8lMwWLgaR7XqK21l9gbS2t8t+5V+QgEK/51zdKk9zomzr27QbcfBtwcKtK2ZU7aJwPZK4H+ioDDu/zf2i+q64WV0qZTGZzdmXJxsUvQdNONgyjXXfBaxuw3vx6G7BY4B820FjuXpNMemLTWgHs6Pr6Qa6mz8i7hV2U0J6prz+fNd1TOLV1heQD9n4wnQTi2wDEwbjNSJqnlZskIcShxHhMqdel5ipQb/pTACtscQ8BHg+Xdwu/DGsB1yZghS3eIGAX1Q8J3jG4L/RZ5vk+LZZl87kuqVSqsHpQXVGKe+tKGdX7p9azUvmCW1R/BbrqM04Gxo4HOrTjtL3hGuDcvxcf7VbFAOlbWwFH0nz3kXJ9dWznbwCXss15gC43LEMp+1pN6wKwqkO2bZ+mgf5V7By9YlhGUbkb9DasJS4nr5UlRkixQ67WopbYF7iPMyzTu6Qek0p1z0ZjgUl5Yzaf696ShtUH7EPZfK5TPBa7yRfcl2fzuW7lyji2mEXAm+ok94V/1eRqnbDjxo2LL128RL066QbGvGwht0VYU7u2AOvL/8o9S0xtwPHqqg4XX3yx955GCDGSGA3+/DxsWOZRbS3C9nznzSJ1YG4ms7enXFOe4OHAD55eunlSEpqyXF6C4qsgJdvWOcDxpwC9SvYIZQb5xmvA9WOBu+4vSnebxtTuGa4zh6XuAFqCBWXXaTO2tlmODwh8acKy/l9LY1tXgFX9cWyhLLc7e32T9FtlWVX+hCXcp0k5xtUU1VtMkoCJYPzCQ35rgPW0ZnyTYVlnNm0QtniKgAO9v1tQpPgLUrHEDxmWSXV1dbtH9YinSCHwiQnLujvcO3UFRIxv4Wuf2wtYBiaalnlWuC7btnfQmG4HQWn6fsy7hX1L79jWPGB5imFZvymleMYW97PS7haJ1Uzp5tj2A4BnbaaocrVhGcW79J+YuA+2hdSnr1I1armoFfVtDk1vbIf2BnbZCxiyDbDNtsCAzYHuPYHqTYp3trlGYPrHwII5QHUc+Pf9gE7A0MHAV18Bb70OTP2y2I2eOhDXS8EadPEtmu96HEi51JBO78GkTfCVciVZ+IaEaZ5HtLLxxroEbMYWzzHwW39uU4ZlXNECS+xlUVtYq4D15Gc/tQRYIcTexJhCurZFIpFoMkXL2PaxDPK0nQz817TM3csROjhhJbivZVlzHVuoPbmKymj9HNueANAZhmVGbNvuo4GUVlqlVk9YKd2LoWlTNZDSCit3Rl2aNHVlNMhBP9c0YAl4PmGZ+6VSqa7Vut6bNW1Xhpb0lUlKfLgqkTQvC9PJscWbADztJxNq2ntPre4dyaUdEcFnLV2t8WaRj8Hc6tVJU1+UUkkBVc1On2rguFOB3x8L7L4nUFXVftzffhNw1pmQjf7iUitQ3QrHY8VHB60lpitpQSEwPyyb066v/7um6YoVjpdkmA6NDiuVbdclYB3bngiQZy7GwHjTMs8rC1ilTaOonsrn862ai+mkPQhgV1Vhi4Atyl5bG5apQNAsObZQVy9FN0It3MmGAOvJbcIWdxFwgipSqpktnqjk7USB3NwewBLhci0SucnNFUYToT8XzfO8+1UQnpPMd5S7/1xdwIYVbc21xPSIugpwbKGOFE8TTsDnkqBU+w+HFU0BIcNabCKclTDNFq85mgPdedxX4i3s3mPTPmeeeWa+dH64d0QA7JnhtZi8U9UF5vhgqh0JXDQS6K5UBz8hjRkNjKwpHhuqquqV2OCWKv89zXeVlrvFlE6nB+ikjwe4VOOlDBgGmqYZiGtYbcAyng2bOYYVg61picOdbm7/TLcYlnF6SzJsxkyarU9UUXP5PBjeNUQ5wBZV1MuXgeloI2kocDdLIi0uIsJY9SMzhJk0rZXyFLXEDwWKFqfe2Q8aqzvEZmWC658OnTpWXXDBBdn6+vqtIpoeePZr9YRVF9WJpNnM8PWq1FU98tHsBQAFctxbTDio2WSu5rVOi4AlvGCY5m+dtHMWiIvP3QiTDNNs8eLSsYUyNPfcQDDjwvZYj6m8ji2UZn5PALl4dVXXQCYO0597RfYCccs2u4qlzbrAQhfYc0fgpluB7dU18BpKMz4Gai4BHnisWGF/dcoqea6Nk5b07WlerlWrO1WdEOJ0YjSzgAP4JcOy9g5GsJqAXerfiDRpr1cHsD7H6IlqrZ6wa8o00Uk7fwLx3UrLBeJlpIzt/MSkjFi4H0Dbej8x5hlJs09LgA3bKjtpMdcz1gaaLJgytniLwUsCGXBVANvaPWxGiKuZcbEPHg9QTZNpOy8DvJf6u533sN5mQ6ztnUgmlFmn0gaG7mFXyLCObf8DIP/OkG8wLMt7IVKanLR4DIRDi7+372LfW6wrdAjqXrd/S0o/7q0rZdfKx6WnVPLB+rdTgIlKgf8zpUcfBmouBKZ/UVS79Y4V2245LYHubkVz0KYfZU9XAVJXJk0scnhDDRtOtHSorDQntneF+UzCMn8aYIV4GowDVP1KbLNqa8f+rNc6GVu8I4tWTW9RoO1qNjr6DmBleFDU6fuasHCWgCVuBljbuQooujUJTnbFDoeBsKYA6zjOYEhuMjkMnlSptsO21NBoq7bu9gLugAm/Nv3XJq0ZTji2Pb1pQwOdaVjGTSsvDjsNkM+Z0BOGZfjgbR08qwDY/wOK1l4rkg5oLjDXBc48Gbhx1V/lrRa0RyUA0VA8ZZUg1aE1Npk+ovmF4mHQRhJCnEy84tFDmFPJ1Nefy5p+vbcdlrF2K1e1Y4sswI8ZluUrCr0Nsl2GE+H6QiKjy/ncdmYq9cnPBlhlXK+T9hUTjmjtUa9j23UB28nAvaZlNlscpTKsGlBDfcO2UnM9DSYzLiHQlyD+Z1hOXlOAbWho6CsLrnrcXdxTwDtZlvWuB9i0eAKEg9X/C9IdWFtb+3lra8NJO8eA+N6wAq41wPo0VPKsN08SvLNlWW83m1THGQjJgYVVPhKLdis1YC/Xp3YDtpw3isBq6ZB9gMfXspPEz2cCKRO4/d7isJQz5cD8ceWBvkDz3SaOqLW5EbZYSEB3b00RLjNN86riHBfnTP2fCGMSplne/1WocnV4lNodrypgw6azYQutnw2wwhY3EHC2uo5pdRE7zpaQHCz0Qry6qnNYngoM5kvfGTq2UG8OhwJQC3oASfeC8OuINQVYpzkgmt5AepNpO2MA/rs3Po0OMgwjbEK50rADI4wwTdoyTQxr0wEs6tCpY28lo4crDyvi2ruo2g3Y0usdBY45ueJd6NzFQFTxqKuXVFSBXDaHfCEPKYuWlkSEaDSK6upq71+L6aUpwKjLgOf9dxN9lDpZLyffPk7z3Wb22eXqdGyhuKjB3jemE4ykcY/6bzqd3kInzbeKoscMyzi8tdGOHj16MzdfmEvgPyUsS3EnXlplwIYUj9l8rmfKD5PyswHWsYVUz7hKjdnLDTZsxUPgUxOW1cRjCSF+T4wHSw2mmxtlA6Ubw5oCbEYIkxm+vS29ZliGUtR4ybbt4RrIf//Y9mR6bDvw74RlNrkcbAuwqp1MWvyTCaf7zb5oWGbwksj7yTfwUI+yizbWkg40ao3Qg4mVqe7YzsO+lnR5vLqqezmlU1CKe3uPAZRNdhEQ6q8n/wMc1D4bDRXyY86cOZg7dy7mz5uPHxf/iB+++wFLly75KpfPz5eu/M5lVz1rK+ikV5NOnapi8U27des+oEu3Lp179+qN/gP6Y8CAAd7LnWbp3rsA5wrgXV9qKQdcwv00z/1jS0DzHnpEY8pIQd0/SSb0aq5cFMr7yvbKTjuez/W9OJUKPyxpVq2TFo+AcHj3HpvGwpr39gJWzeWSxUseCWwUSjnUsg/YA41UazuJ+ubYQhkxePenYXO5hnR6N0na62H2sbW6hBB/JIb3VrH0ftVJO38A8QNMaGY/62uglR1NrJySLHytw8CbpmV6109BCrM65V7reLticy1iTpPuDqVPnhzbuQ3gU7y+S/eicg+glfmgG82/xsBWkVi0Y5hlLXle97Jhmd5jgtIUvm8tZ85p23ZvjUmx6N7D7raueJy0eNc3ClnWvcemXctd64QAq/wUHeaxnup0PWR34PGyD4Gaur18+XJ8/PHH+OTjT/Dl7Nn45ttv0djYqDa3F+LR+Ct6TJ/qOE7TA/ByY1Y+mBZ/v3h7l91h8er4fr169Pz15ltu0X/boUMxdNttEYlEVhS7/RZgjAO85zuTKGWVJR6kb9wmmbLZWgjNIRNOM02zmQZNGV1I0l5VZZTNQDQW3a+c2OHYTi3AdaXcXhEr9niAik/zyrzs8t59u+5JrOnqvbfaleZA0qmlG++KEzZsQN7OVw1hNoIJw0zT9ORKxxaeHWpb7HBzogmlSvAMMSR4P8uynlf/D96tlnNBE2wYWkTvV1NTExhJeNU6zVnt2YZlFu9V/eSkneNAHLAsSxh4mBh5ECm+avPQe1g1S09p7F5Q7n2iB2xbTCLg2GLV9DEzTyKiryVkJw3YGyDvKCq1RVa/1dXV7RTVI4FcOt2wTM/AvzT55pzqbPONVVZ+EujRS4ixzPCcDxDwA4Mnqk1QEi0hSVsy8a8I3ntYNfcv+8YWrbpb4V7axSC6uul0feUFYM+VDLK8Ls+bNw9vv/023n9vqvd/5eisU6fOk+LV8buSvgF7ufG157djjjlG79u372EEGtG/f7+jd9xxeMfhOw1Hjx7Fw99LN4wDbrwGeN+XspR+WxldKFPGRe5jd15qnvHw8OELdps1qyqfzw8n9vw8eS+TiDE6kTS997OlSQjxZ3X9FxgTKes4YvqANHYlY5hvG9AN4HrDspTjhGYpvLEr0APwdhYCdSHwdmoz9wsUiHGNHo+mym0KK3w6Oc5gcvkMJopqUvtHe/zSOI5zMCQOlpBf5vP5awOjcyXbEeRrCcvyNQNtT4dysQHpXU9ITRYmBuAoypDyL9l8/qpUKqVO1KaUSWd+7ZK7u2VZV5e2oLzbzfhkxoVEtDkTP2ea5sPhPI73ZlZeAmjKqrUbg/uQumhSPieKpo+zAO0NTRYmtwTUZn3xHtprxwOsdvEmH78MzCTwndl8XpTzGDFx4sTo9wsXKkVGb3bpEaPWeK4lahXfzuonKI8dBJpa6kUjKKc2K2I+AYxjQqZ46kGAEhRnAzQl7+ZvHDVqVKseG4L6uHdkf2jaM5ibA/YZCkxe2WWRirfz8ksvY+rUqfjxxx/RvWu3adWbbDIum8/e3pYnjrZXx8o5UqlU94ULFh7TtXvXPw8bNmz3nXb+JbYeMmRFxrtvByZeD0zxh6hmRAeWbLFlfswJ58x9a7N+3bdd+E3HrsuVLzaeQqyPSSQTbRlcbKETne6bgioWOUjfqzokUFeqFAwyZDKZHdnlk4lYZ+YtGNSR1FqTkNCwkIF3C4XC81LKt8JPJ0tHXnFzujqrpY0ySiYCEEmlUmo1rPOkHg80NjbqpRteezvGvTAIEX2GZ82kTAdPVp5Oikl5hXji8SfwysuvIJfNqtNujhbVay3LuqW99f/UfBeee+GB0Vj0oq232frQPffaA9v/wjNvL6YpLwDjxwD3P7LiEUKfGJ4/+Ji614YMm/RNVdWisRdf3HQLsCp9Ue59OnfunGtNnFiV+tqTtwLY9lBpI8/Dig2vxleIoQ9mzAd6KDdRwDtvv4Mnn3gCc+fMRY9ePVEdi2ciVbG61hRYPycpL7nkkl2l6567+YDNT9ph+HB9u113xWadfGZnwXzgnjuABycBk5X5NZQQPoKUrLgBpQpgN6DJWpddZeAFHLHPb/DwZORdF5PuuQevv/Y6OnXshK7dujzPOZzflhO+tdV/y7K2WLxo8eldu3X981ZbbdV/q6FDsdnOu6BfLFKUVd55A3jqCeDufwFzZp9F37bsZmZt9bm97VQA215KbeT5lFELbr3hmFknnolJY67GrC++QP9+/aDrWqrGMK5YH8mj9AMzPplxaj6fP6aqumr/zl266F369UN04GBwPAb66CP8+OknWB6vei4Wi5yofAyvj+MI96kC2PV9htaT/jFw3ac33XDeVdHO6Dz1XfTq3fPzgnRPbc1Vz3rSda8bDZdf3n+ZxH65XG7HQr4wCDr14o6dZFWHjl93XN64uABZ35YfrPVhPBXArg+zsAH04Y3jjrzs9u12Hd25UECnTaqficVjR64rWXUDINfP1sUKYH820v5vVXzOdRNH9ln8fUPMzSt/uWvEq8X/FoXWzmgqgF07dN7gWykaDvCgtnxCb/ADXc8HUAHsej5Ble5VKFBROlXWQIUCGygFKifsBjpxlW5vnBSoAHbjnPfKqDdQClQAu4FOXKXbGycFKoDdOOe9MuoNlAIVwG6gE1fp9sZJgQpgN855r4x6A6VABbAlE1f0RCEPkMDLLUU7V+5pcsuXXyiBf4R9/wRVKUfgGsmZLcUAXVNrxbbt7TXWtjWShudep6VUjDnEdSDqBuYYMf2wvJC7dHXfx66p/lfqWXUKVAAbopkXj8fzi0Q3EPjsvHSPLue6NJVKVcWjscZyjqWVH6KqWHxRaSDeVZ+atkv4oRRPKnXKFi7ped74dMZrxPiQiO9xgRwRdYpGo0+3xx1q272o5FibFKgAtjlgT9OAww3L+qMKRMREb5qmqfz4NEuewzOQiiz2tWmZvwt/zNj2KQy6jVgemUgmHyluAtoIEDYlYpdc976wy5mMbZ/A0IYw86LBWw++7thjj3W9EzyX21pK2U8DBqh4OcVTklTYhghBfq48S3o+m4HjDdP0Yg0JIVQM0W/CMXgynusamOHwE+H++q559iTivMv8sGVZH6jvng+peLw7Mw8lph3BmJ4tZB+pikb3Z2jDSRaWBIGj1QZWpVUNkhE5xM/7jZE0VDwgqJAnhVjuGGZSr96lxu4TNcmk94JcjSniut0l0VBo2o5g/iJhWXcqf8xqnOHXM4qOESk7t8ddz9oE0NpuqwLYEMWFLW7UGIuUI66MEElmGmJYxqllALs9ER1KwHBi/k/guyqVSkXi0WgdMfVi0Ntq0Y6urx/iatqfAa2RmTfRCL9zwacqYDi2nQFoD4BUrKAtAe6h4ruqsJoRPXI9g+/VgE7k6pNY5ysB+S6gZRXwawzDbhDiUCY6UQHWj8fzV026JzbbEOrrL2RdH2yY5vml4/BduP6JCPcxs3JrczSkdoHy1Of1jWkYA88TUQflEpWBTxn8rgZN5T2cwe+YlnlOxrYPY9AVzLhTnd4ADgXxTMM0Tyr69aUziWh5sQ06ggnnqWd5nutPxlahNo4ncANr2hS4PNFImgcFfc7/EPhbAAAGY0lEQVTY4j5JeNw0TT/I8dqGyvrRXgWwoXlQ/n/1QtS8LHXZglQq1TEejd+dMBNHlcYNzdRlhiEiR4D5Iwn6g2mZyguh8hJ/HgidmPg9YtrJsAzfn/GKRopeDenDeHX8jmxj9v5waA3l01aDtLNS5qO6fpZhWZ7zJK9ejc8yTDPs+MvzKAmigS7zyxrT1axh/1KZ2rbtSzRoAwzL8DwpBkk97v7u22/fY6KjTdP8SP2eqa8/nzX9ALVpCFtcT0zTg5MyI8SZkNg5CBrmyc/AeBXLyPNsyXSAkTRPC+p3VNwhDSeWhi9RAdCUwzkVbC2TFrdAw+tBxD0n7ZwIwp+Us27lN5kgJyQs64niphcZO2jIoKMUB7J+QGfd9KICWJ/uqVRqk3g0/jYzP6hOMGZSTr//qkX1XWtqar4KT48QYjuSGKkWqCPEs5qURk0y+V/Hdh7VZeFCqWm7g2jLhGkKVc4Lbwh9N9a4KzGfknfdkdFo9BNI+TBYmyRJVqtNQWOcQyxPcDXtO00ikUiaf/FZx55g3EGMeazhg2g0OkHJn5l0ei8mbRIYU1ty2C7S4mLlObIUsP4YrjaS5iFNIKt39oWGS4uAUSesNrsJsPX1F4L0voEb0Ew6s48kea4KrVL08axEiRXciH8i3qbCtCjWF567V3QjphES8t9KoedvCh8YSeNGb2OyHRVB8FeqHn+j2U6FWBRpcYUGbFIaG3fdQGbdtloBrE9/IcTRxLgUTHdKLsQ1imRBOJGI70yYZjH044q82xGQVKxoka0kIp2uZ9f9lwqA5LPTrmEZTsa2j2doJwHyA2ZSdR7M4LOr8/kvstHog0x0J0mKExeIKbLASBqTnHpnXyI+JQBs0K5t26fpTL9mwlDStcNyudzAqB65FoR5klm52PTkz3BSwZxA+k6JpOlHwit+9aIWMDllADtSnfoKsCTll4GcWgyEHOljWIYXMNm27d9qRGcbpnlsOcCqyPDk6rUyIruCcTmBle/l5QTah5luNpLGXQqwGmFaQF+PrQfvoTZCFdS6Khq7eeCQwcfO/PTTGyUwPohptG4hs25brwDWp7+TFrdK4mmWZV0ZAuafNcah4dAa/omnAGsqGS2TyXRBQSZBGMjwosf9MyOEciSdS5hmJmOLZ8BaKggvqbzDK6WRHos9WMgVJpWL1aLCk2gSR5YCtukkFOL/IEmdzLM0aIcw8YMk8azG7r6lShlfHr7LtMxi3Bg/KRedhXz+1Ug0umegLS5GWcAZRcA6o0kWZrUHsIollqDdTMu8oKmPafFYtpA7Kh6JPcQa7g286at3tRrQL2Ga6dYAq+opetKXOxHRfxUt1y1U1o/WK4AF4Mlz3yx8A0wXGbXGCyHADlXBpKHRHoZhfB866VRM12uC6xTHdv4F8GlBpANHiOsIKCRM8+/K47ty/A3yQpF0ImaDgIzS8qpNAhoGQNJNrHGMJHVKWIkJjuMcRcC5hmkeqNpUYUekrh/HkmYqGRng86HRiKIGF0nDMvfwQ49MZMJRpX6W/Ch73QisNLcFZq37oK0HTZjx6QwVb3QPMF1NJOMSNAqEegWuYoAt+kRFsy+CxxYoysInq78z6fQRkrSkaZm7K/aYNamCn40H80KAVOygiIqP6tGGWEW1H68xd2TQeRJ8n3L+nrHFgyC8pcDrA9QC8X6Gae7vn+JKGz+PCX8wTfM/6wdk1m0vKoAF4J022cLhih0tnQ4FBD2mvxj2qCeE6KlkrWARqcBbzNwj8KQvhNhbkxqrU7UYMpJGERO5xB9rrM1x4b6iriyYmRpsZzQDPb2wbYACiJ3JZDaXUg4PohV4MjBRAkwdVD6CvDdhWY/5hhNDguj23hURaxxEXguPRZ2YAPpAieZMWS2iXVRTU7NYpIVNQD9Vr4ScHDgAd+qdA/KcXxSMSZ3UUYp2CmK9qOgCzLyLaZr/9thjkEOEl1liUwJkrJC7VAWN8iIssIo3g7jUMIMkfa1z4bWRtbUz1ZVTznUXjBo16i3V17q6up1jWqx/4IHfuy6Kxh6N5GPHX5q6tM3gzOsWSmun9Qpg1w6d/6dbyairI03bW91fr8mBKo26ZERNyzxvTda7IddVAeyGPHvrSd89jTHkL82kec2a7JJjOzUau88rDfyarHdDrqsC2A159ip93+goUAHsRjfllQFvyBT4/3CUeF7qsZkDAAAAAElFTkSuQmCC">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F335453-0BB5-BE9B-51AF-1CC1D6E98ABD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BD3D6E5-2E83-2EEA-22BC-9B91F48F2A45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1268,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA54B76-CACA-46D9-9A5A-651145811BAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F82737B7-772E-4AAF-9821-8E8AAD899046}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2396,7 +2396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE30B94-6F29-44B6-8036-6928AD061F4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D15BE87-A9BE-460B-8938-FE6A3646659E}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2535,7 +2535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7090C1-D5F7-4446-A064-158C319A0AA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1C4D18-5321-496B-AB78-C88E830299E5}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2845,7 +2845,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB3A2415-F101-4F86-8398-D4E338A7234B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80058898-EA56-441A-ACF8-C7D5F281E473}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
